--- a/Config/Luban/Datas/gamecore/action_spec.xlsx
+++ b/Config/Luban/Datas/gamecore/action_spec.xlsx
@@ -1,14 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_Project_1\DG\Config\Luban\Datas\gamecore\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135688C7-6702-4BC8-8CC7-02C88E2DE4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="action_spec" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -271,34 +283,382 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V12"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="30.26953125" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" customWidth="1"/>
+    <col min="9" max="9" width="28.7265625" customWidth="1"/>
+    <col min="11" max="11" width="22.81640625" customWidth="1"/>
+    <col min="12" max="12" width="20.26953125" customWidth="1"/>
+    <col min="13" max="13" width="21.81640625" customWidth="1"/>
+    <col min="14" max="14" width="19.81640625" customWidth="1"/>
+    <col min="16" max="16" width="18.26953125" customWidth="1"/>
+    <col min="17" max="17" width="27.81640625" customWidth="1"/>
+    <col min="18" max="18" width="20.1796875" customWidth="1"/>
+    <col min="19" max="19" width="20.26953125" customWidth="1"/>
+    <col min="20" max="20" width="23.26953125" customWidth="1"/>
+    <col min="21" max="21" width="15.08984375" customWidth="1"/>
+    <col min="22" max="22" width="21.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
@@ -1117,6 +1477,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Config/Luban/Datas/gamecore/action_spec.xlsx
+++ b/Config/Luban/Datas/gamecore/action_spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_Project_1\DG\Config\Luban\Datas\gamecore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135688C7-6702-4BC8-8CC7-02C88E2DE4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5644FF1A-C98F-4EC1-9BFD-2C57E05C2053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -656,7 +656,7 @@
     <col min="18" max="18" width="20.1796875" customWidth="1"/>
     <col min="19" max="19" width="20.26953125" customWidth="1"/>
     <col min="20" max="20" width="23.26953125" customWidth="1"/>
-    <col min="21" max="21" width="15.08984375" customWidth="1"/>
+    <col min="21" max="21" width="44.6328125" customWidth="1"/>
     <col min="22" max="22" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Config/Luban/Datas/gamecore/action_spec.xlsx
+++ b/Config/Luban/Datas/gamecore/action_spec.xlsx
@@ -507,7 +507,7 @@
           <t>target_rule</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>targeting_id</t>
         </is>
@@ -624,7 +624,7 @@
           <t>ActionTargetRule</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -741,7 +741,7 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -850,7 +850,7 @@
           <t>TargetCoordOneStep</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>legacy_target_coord_one_step</t>
         </is>
@@ -951,7 +951,7 @@
           <t>DirectionFromComponent</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>legacy_direction_component_cell</t>
         </is>
@@ -1060,7 +1060,7 @@
           <t>DirectionFromRequest</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>legacy_direction_cell</t>
         </is>
@@ -1118,7 +1118,7 @@
       <c r="V6" s="0" t="inlineStr"/>
       <c r="W6" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
           <t>TargetCoordAny</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>legacy_target_coord_any</t>
         </is>
@@ -1254,7 +1254,7 @@
           <t>TargetCoordAny</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>legacy_target_coord_any</t>
         </is>
@@ -1347,7 +1347,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>legacy_none</t>
         </is>
@@ -1448,7 +1448,7 @@
           <t>DirectionFromRequest</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>legacy_direction_cell</t>
         </is>
@@ -1553,7 +1553,7 @@
           <t>DirectionFromRequest</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>legacy_direction_cell</t>
         </is>
@@ -1654,7 +1654,7 @@
           <t>DirectionFromRequest</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>legacy_direction_cell</t>
         </is>

--- a/Config/Luban/Datas/gamecore/action_spec.xlsx
+++ b/Config/Luban/Datas/gamecore/action_spec.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28.6328125" customWidth="1" style="1" min="2" max="2"/>
@@ -504,70 +504,65 @@
       </c>
       <c r="J1" s="0" t="inlineStr">
         <is>
-          <t>target_rule</t>
+          <t>targeting_id</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
         <is>
-          <t>targeting_id</t>
+          <t>handoff_policy</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
         <is>
-          <t>handoff_policy</t>
+          <t>blocked_result_policy_id</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
         <is>
-          <t>blocked_result_policy_id</t>
+          <t>handoff_spec_id</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
         <is>
-          <t>handoff_spec_id</t>
+          <t>handoff_subject_policy</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
         <is>
-          <t>handoff_subject_policy</t>
+          <t>max_chain_depth</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
         <is>
-          <t>max_chain_depth</t>
+          <t>conflict_policy</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
         <is>
-          <t>conflict_policy</t>
+          <t>interrupt_policy</t>
         </is>
       </c>
       <c r="R1" s="0" t="inlineStr">
         <is>
-          <t>interrupt_policy</t>
+          <t>merge_policy</t>
         </is>
       </c>
       <c r="S1" s="0" t="inlineStr">
         <is>
-          <t>merge_policy</t>
+          <t>subject_policy</t>
         </is>
       </c>
       <c r="T1" s="0" t="inlineStr">
         <is>
-          <t>subject_policy</t>
+          <t>plan_rule</t>
         </is>
       </c>
       <c r="U1" s="0" t="inlineStr">
         <is>
-          <t>plan_rule</t>
+          <t>commit_rules</t>
         </is>
       </c>
       <c r="V1" s="0" t="inlineStr">
-        <is>
-          <t>commit_rules</t>
-        </is>
-      </c>
-      <c r="W1" s="0" t="inlineStr">
         <is>
           <t>default_cost_ticks</t>
         </is>
@@ -621,19 +616,19 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>ActionTargetRule</t>
+          <t>string</t>
         </is>
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
+          <t>ActionHandoffPolicy</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>ActionHandoffPolicy</t>
-        </is>
-      </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
           <t>string</t>
@@ -641,50 +636,45 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>ActionSubjectPolicy</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>ActionConflictPolicy</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t>ActionInterruptPolicy</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>ActionMergePolicy</t>
+        </is>
+      </c>
+      <c r="S2" s="0" t="inlineStr">
+        <is>
           <t>ActionSubjectPolicy</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Q2" s="0" t="inlineStr">
-        <is>
-          <t>ActionConflictPolicy</t>
-        </is>
-      </c>
-      <c r="R2" s="0" t="inlineStr">
-        <is>
-          <t>ActionInterruptPolicy</t>
-        </is>
-      </c>
-      <c r="S2" s="0" t="inlineStr">
-        <is>
-          <t>ActionMergePolicy</t>
-        </is>
-      </c>
       <c r="T2" s="0" t="inlineStr">
         <is>
-          <t>ActionSubjectPolicy</t>
+          <t>ActionPlanRule</t>
         </is>
       </c>
       <c r="U2" s="0" t="inlineStr">
         <is>
-          <t>ActionPlanRule</t>
+          <t>(list#sep=,),ActionCommitRule</t>
         </is>
       </c>
       <c r="V2" s="0" t="inlineStr">
-        <is>
-          <t>(list#sep=,),ActionCommitRule</t>
-        </is>
-      </c>
-      <c r="W2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -797,11 +787,6 @@
         </is>
       </c>
       <c r="V3" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="W3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -847,66 +832,61 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>TargetCoordOneStep</t>
+          <t>legacy_target_coord_one_step</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>legacy_target_coord_one_step</t>
+          <t>Configured</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t>Configured</t>
+          <t>push_or_block</t>
         </is>
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
-          <t>push_or_block</t>
+          <t>player_push</t>
         </is>
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t>player_push</t>
+          <t>ConnectedBodyIfAny</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="inlineStr">
+        <is>
+          <t>ExclusiveTargetCell</t>
+        </is>
+      </c>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t>HigherPriorityInterruptsLower</t>
+        </is>
+      </c>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t>SameClaim</t>
+        </is>
+      </c>
+      <c r="S4" s="0" t="inlineStr">
+        <is>
           <t>ConnectedBodyIfAny</t>
         </is>
       </c>
-      <c r="P4" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q4" s="0" t="inlineStr">
-        <is>
-          <t>ExclusiveTargetCell</t>
-        </is>
-      </c>
-      <c r="R4" s="0" t="inlineStr">
-        <is>
-          <t>HigherPriorityInterruptsLower</t>
-        </is>
-      </c>
-      <c r="S4" s="0" t="inlineStr">
-        <is>
-          <t>SameClaim</t>
-        </is>
-      </c>
       <c r="T4" s="0" t="inlineStr">
         <is>
-          <t>ConnectedBodyIfAny</t>
-        </is>
-      </c>
-      <c r="U4" s="0" t="inlineStr">
-        <is>
           <t>MoveBody</t>
         </is>
       </c>
-      <c r="V4" s="0" t="inlineStr"/>
-      <c r="W4" s="0" t="inlineStr">
+      <c r="U4" s="0" t="inlineStr"/>
+      <c r="V4" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -948,70 +928,65 @@
       <c r="I5" s="0" t="inlineStr"/>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>DirectionFromComponent</t>
+          <t>legacy_direction_component_cell</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>legacy_direction_component_cell</t>
+          <t>Configured</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t>Configured</t>
+          <t>bounce_or_block</t>
         </is>
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t>bounce_or_block</t>
+          <t>mechanism_push</t>
         </is>
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t>mechanism_push</t>
+          <t>ConnectedBodyIfAny</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
         <is>
-          <t>ConnectedBodyIfAny</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ExclusiveTargetCell</t>
         </is>
       </c>
       <c r="Q5" s="0" t="inlineStr">
         <is>
-          <t>ExclusiveTargetCell</t>
+          <t>HigherPriorityInterruptsLower</t>
         </is>
       </c>
       <c r="R5" s="0" t="inlineStr">
         <is>
-          <t>HigherPriorityInterruptsLower</t>
+          <t>SameClaim</t>
         </is>
       </c>
       <c r="S5" s="0" t="inlineStr">
         <is>
-          <t>SameClaim</t>
+          <t>HitEntity</t>
         </is>
       </c>
       <c r="T5" s="0" t="inlineStr">
         <is>
-          <t>HitEntity</t>
+          <t>MoveBody</t>
         </is>
       </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
-          <t>MoveBody</t>
+          <t>SetAutoMoveTick,SetDirectionOnBounce</t>
         </is>
       </c>
       <c r="V5" s="0" t="inlineStr">
-        <is>
-          <t>SetAutoMoveTick,SetDirectionOnBounce</t>
-        </is>
-      </c>
-      <c r="W5" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1057,66 +1032,61 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>DirectionFromRequest</t>
+          <t>legacy_direction_cell</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>legacy_direction_cell</t>
+          <t>Configured</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t>Configured</t>
+          <t>immune_push_or_block</t>
         </is>
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t>immune_push_or_block</t>
+          <t>mechanism_push</t>
         </is>
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t>mechanism_push</t>
+          <t>ConnectedBodyIfAny</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P6" s="0" t="inlineStr">
+        <is>
+          <t>ExclusiveTargetCell</t>
+        </is>
+      </c>
+      <c r="Q6" s="0" t="inlineStr">
+        <is>
+          <t>HigherPriorityInterruptsLower</t>
+        </is>
+      </c>
+      <c r="R6" s="0" t="inlineStr">
+        <is>
+          <t>SameClaim</t>
+        </is>
+      </c>
+      <c r="S6" s="0" t="inlineStr">
+        <is>
           <t>ConnectedBodyIfAny</t>
         </is>
       </c>
-      <c r="P6" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q6" s="0" t="inlineStr">
-        <is>
-          <t>ExclusiveTargetCell</t>
-        </is>
-      </c>
-      <c r="R6" s="0" t="inlineStr">
-        <is>
-          <t>HigherPriorityInterruptsLower</t>
-        </is>
-      </c>
-      <c r="S6" s="0" t="inlineStr">
-        <is>
-          <t>SameClaim</t>
-        </is>
-      </c>
       <c r="T6" s="0" t="inlineStr">
         <is>
-          <t>ConnectedBodyIfAny</t>
-        </is>
-      </c>
-      <c r="U6" s="0" t="inlineStr">
-        <is>
           <t>MoveBody</t>
         </is>
       </c>
-      <c r="V6" s="0" t="inlineStr"/>
-      <c r="W6" s="0" t="inlineStr">
+      <c r="U6" s="0" t="inlineStr"/>
+      <c r="V6" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1158,62 +1128,57 @@
       <c r="I7" s="0" t="inlineStr"/>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t>TargetCoordAny</t>
+          <t>legacy_target_coord_any</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>legacy_target_coord_any</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M7" s="0" t="inlineStr">
-        <is>
           <t>reject_only</t>
         </is>
       </c>
-      <c r="N7" s="0" t="inlineStr"/>
+      <c r="M7" s="0" t="inlineStr"/>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>HitEntity</t>
+        </is>
+      </c>
       <c r="O7" s="0" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" s="0" t="inlineStr">
+        <is>
+          <t>ExclusiveTargetCell</t>
+        </is>
+      </c>
+      <c r="Q7" s="0" t="inlineStr">
+        <is>
+          <t>HigherPriorityInterruptsLower</t>
+        </is>
+      </c>
+      <c r="R7" s="0" t="inlineStr">
+        <is>
+          <t>SameClaim</t>
+        </is>
+      </c>
+      <c r="S7" s="0" t="inlineStr">
+        <is>
           <t>HitEntity</t>
         </is>
       </c>
-      <c r="P7" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" s="0" t="inlineStr">
-        <is>
-          <t>ExclusiveTargetCell</t>
-        </is>
-      </c>
-      <c r="R7" s="0" t="inlineStr">
-        <is>
-          <t>HigherPriorityInterruptsLower</t>
-        </is>
-      </c>
-      <c r="S7" s="0" t="inlineStr">
-        <is>
-          <t>SameClaim</t>
-        </is>
-      </c>
       <c r="T7" s="0" t="inlineStr">
         <is>
-          <t>HitEntity</t>
-        </is>
-      </c>
-      <c r="U7" s="0" t="inlineStr">
-        <is>
           <t>MoveBody</t>
         </is>
       </c>
-      <c r="V7" s="0" t="inlineStr"/>
-      <c r="W7" s="0" t="inlineStr">
+      <c r="U7" s="0" t="inlineStr"/>
+      <c r="V7" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1251,62 +1216,57 @@
       <c r="I8" s="0" t="inlineStr"/>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>TargetCoordAny</t>
+          <t>legacy_target_coord_any</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>legacy_target_coord_any</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
+          <t>reject_only</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr"/>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t>HitEntity</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="M8" s="0" t="inlineStr">
-        <is>
-          <t>reject_only</t>
-        </is>
-      </c>
-      <c r="N8" s="0" t="inlineStr"/>
-      <c r="O8" s="0" t="inlineStr">
+      <c r="Q8" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R8" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S8" s="0" t="inlineStr">
         <is>
           <t>HitEntity</t>
         </is>
       </c>
-      <c r="P8" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R8" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S8" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="T8" s="0" t="inlineStr">
         <is>
-          <t>HitEntity</t>
-        </is>
-      </c>
-      <c r="U8" s="0" t="inlineStr">
-        <is>
           <t>SpawnEntity</t>
         </is>
       </c>
-      <c r="V8" s="0" t="inlineStr"/>
-      <c r="W8" s="0" t="inlineStr">
+      <c r="U8" s="0" t="inlineStr"/>
+      <c r="V8" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1344,62 +1304,57 @@
       <c r="I9" s="0" t="inlineStr"/>
       <c r="J9" s="0" t="inlineStr">
         <is>
+          <t>legacy_none</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>legacy_none</t>
-        </is>
-      </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
+          <t>reject_only</t>
+        </is>
+      </c>
+      <c r="M9" s="0" t="inlineStr"/>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>HitEntity</t>
+        </is>
+      </c>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="M9" s="0" t="inlineStr">
-        <is>
-          <t>reject_only</t>
-        </is>
-      </c>
-      <c r="N9" s="0" t="inlineStr"/>
-      <c r="O9" s="0" t="inlineStr">
+      <c r="Q9" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R9" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S9" s="0" t="inlineStr">
         <is>
           <t>HitEntity</t>
         </is>
       </c>
-      <c r="P9" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R9" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S9" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="T9" s="0" t="inlineStr">
         <is>
-          <t>HitEntity</t>
-        </is>
-      </c>
-      <c r="U9" s="0" t="inlineStr">
-        <is>
           <t>RemoveEntity</t>
         </is>
       </c>
-      <c r="V9" s="0" t="inlineStr"/>
-      <c r="W9" s="0" t="inlineStr">
+      <c r="U9" s="0" t="inlineStr"/>
+      <c r="V9" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1445,66 +1400,61 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>DirectionFromRequest</t>
+          <t>legacy_direction_cell</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>legacy_direction_cell</t>
+          <t>Configured</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t>Configured</t>
+          <t>push_or_block</t>
         </is>
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>push_or_block</t>
+          <t>player_push</t>
         </is>
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>player_push</t>
+          <t>ConnectedBodyIfAny</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="inlineStr">
+        <is>
+          <t>ExclusiveTargetCell</t>
+        </is>
+      </c>
+      <c r="Q10" s="0" t="inlineStr">
+        <is>
+          <t>HigherPriorityInterruptsLower</t>
+        </is>
+      </c>
+      <c r="R10" s="0" t="inlineStr">
+        <is>
+          <t>SameClaim</t>
+        </is>
+      </c>
+      <c r="S10" s="0" t="inlineStr">
+        <is>
           <t>ConnectedBodyIfAny</t>
         </is>
       </c>
-      <c r="P10" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q10" s="0" t="inlineStr">
-        <is>
-          <t>ExclusiveTargetCell</t>
-        </is>
-      </c>
-      <c r="R10" s="0" t="inlineStr">
-        <is>
-          <t>HigherPriorityInterruptsLower</t>
-        </is>
-      </c>
-      <c r="S10" s="0" t="inlineStr">
-        <is>
-          <t>SameClaim</t>
-        </is>
-      </c>
       <c r="T10" s="0" t="inlineStr">
         <is>
-          <t>ConnectedBodyIfAny</t>
-        </is>
-      </c>
-      <c r="U10" s="0" t="inlineStr">
-        <is>
           <t>MoveBody</t>
         </is>
       </c>
-      <c r="V10" s="0" t="inlineStr"/>
-      <c r="W10" s="0" t="inlineStr">
+      <c r="U10" s="0" t="inlineStr"/>
+      <c r="V10" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1550,66 +1500,61 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>DirectionFromRequest</t>
+          <t>legacy_direction_cell</t>
         </is>
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>legacy_direction_cell</t>
+          <t>Configured</t>
         </is>
       </c>
       <c r="L11" s="0" t="inlineStr">
         <is>
-          <t>Configured</t>
+          <t>immune_push_or_block</t>
         </is>
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>immune_push_or_block</t>
+          <t>configured_wind_push</t>
         </is>
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t>configured_wind_push</t>
+          <t>ConnectedBodyIfAny</t>
         </is>
       </c>
       <c r="O11" s="0" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P11" s="0" t="inlineStr">
+        <is>
+          <t>ExclusiveTargetCell</t>
+        </is>
+      </c>
+      <c r="Q11" s="0" t="inlineStr">
+        <is>
+          <t>HigherPriorityInterruptsLower</t>
+        </is>
+      </c>
+      <c r="R11" s="0" t="inlineStr">
+        <is>
+          <t>SameClaim</t>
+        </is>
+      </c>
+      <c r="S11" s="0" t="inlineStr">
+        <is>
           <t>ConnectedBodyIfAny</t>
         </is>
       </c>
-      <c r="P11" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q11" s="0" t="inlineStr">
-        <is>
-          <t>ExclusiveTargetCell</t>
-        </is>
-      </c>
-      <c r="R11" s="0" t="inlineStr">
-        <is>
-          <t>HigherPriorityInterruptsLower</t>
-        </is>
-      </c>
-      <c r="S11" s="0" t="inlineStr">
-        <is>
-          <t>SameClaim</t>
-        </is>
-      </c>
       <c r="T11" s="0" t="inlineStr">
         <is>
-          <t>ConnectedBodyIfAny</t>
-        </is>
-      </c>
-      <c r="U11" s="0" t="inlineStr">
-        <is>
           <t>MoveBody</t>
         </is>
       </c>
-      <c r="V11" s="0" t="inlineStr"/>
-      <c r="W11" s="0" t="inlineStr">
+      <c r="U11" s="0" t="inlineStr"/>
+      <c r="V11" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1651,66 +1596,61 @@
       <c r="I12" s="0" t="inlineStr"/>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>DirectionFromRequest</t>
+          <t>legacy_direction_cell</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>legacy_direction_cell</t>
+          <t>Configured</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t>Configured</t>
+          <t>push_or_block</t>
         </is>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>push_or_block</t>
+          <t>connected_body_move</t>
         </is>
       </c>
       <c r="N12" s="0" t="inlineStr">
         <is>
-          <t>connected_body_move</t>
+          <t>ConnectedBodyIfAny</t>
         </is>
       </c>
       <c r="O12" s="0" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P12" s="0" t="inlineStr">
+        <is>
+          <t>ExclusiveTargetCell</t>
+        </is>
+      </c>
+      <c r="Q12" s="0" t="inlineStr">
+        <is>
+          <t>HigherPriorityInterruptsLower</t>
+        </is>
+      </c>
+      <c r="R12" s="0" t="inlineStr">
+        <is>
+          <t>SameClaim</t>
+        </is>
+      </c>
+      <c r="S12" s="0" t="inlineStr">
+        <is>
           <t>ConnectedBodyIfAny</t>
         </is>
       </c>
-      <c r="P12" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q12" s="0" t="inlineStr">
-        <is>
-          <t>ExclusiveTargetCell</t>
-        </is>
-      </c>
-      <c r="R12" s="0" t="inlineStr">
-        <is>
-          <t>HigherPriorityInterruptsLower</t>
-        </is>
-      </c>
-      <c r="S12" s="0" t="inlineStr">
-        <is>
-          <t>SameClaim</t>
-        </is>
-      </c>
       <c r="T12" s="0" t="inlineStr">
         <is>
-          <t>ConnectedBodyIfAny</t>
-        </is>
-      </c>
-      <c r="U12" s="0" t="inlineStr">
-        <is>
           <t>MoveBody</t>
         </is>
       </c>
-      <c r="V12" s="0" t="inlineStr"/>
-      <c r="W12" s="0" t="inlineStr">
+      <c r="U12" s="0" t="inlineStr"/>
+      <c r="V12" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
